--- a/04_Figures/F04_association/modules/total/limma/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/total/limma/c_data/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -492,16 +486,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000790318825204221</v>
+        <v>-0.00583363322851157</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.119769560670013</v>
+        <v>-0.864323506486184</v>
       </c>
       <c r="F2" t="n">
-        <v>0.904819800940496</v>
+        <v>0.388978138724852</v>
       </c>
       <c r="G2" t="n">
-        <v>0.91390595889334</v>
+        <v>0.713126587662229</v>
       </c>
     </row>
     <row r="3">
@@ -515,16 +509,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00950648125756549</v>
+        <v>-0.000246884250041642</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.44066805373403</v>
+        <v>-0.0365788955756221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.151682547163024</v>
+        <v>0.970876031195111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.604182835882824</v>
+        <v>0.970876031195111</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +532,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00825168229819739</v>
+        <v>-0.0110111291044082</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.25050844308086</v>
+        <v>-1.63143230729342</v>
       </c>
       <c r="F4" t="n">
-        <v>0.21298630742084</v>
+        <v>0.105182718544302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.604182835882824</v>
+        <v>0.578504951993659</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000747829370738535</v>
+        <v>0.00660236015267749</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.113330458965522</v>
+        <v>0.978219722548941</v>
       </c>
       <c r="F5" t="n">
-        <v>0.909914284148543</v>
+        <v>0.329755078496618</v>
       </c>
       <c r="G5" t="n">
-        <v>0.91390595889334</v>
+        <v>0.713126587662229</v>
       </c>
     </row>
     <row r="6">
@@ -584,16 +578,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000714559533655517</v>
+        <v>0.00082957191142914</v>
       </c>
       <c r="E6" t="n">
-        <v>0.108288552276831</v>
+        <v>0.122911138784744</v>
       </c>
       <c r="F6" t="n">
-        <v>0.91390595889334</v>
+        <v>0.902364408028921</v>
       </c>
       <c r="G6" t="n">
-        <v>0.91390595889334</v>
+        <v>0.970876031195111</v>
       </c>
     </row>
     <row r="7">
@@ -607,16 +601,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00769712540060076</v>
+        <v>-0.000610774408096603</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.16646763084978</v>
+        <v>-0.0904936353382596</v>
       </c>
       <c r="F7" t="n">
-        <v>0.245205552247277</v>
+        <v>0.928032124997603</v>
       </c>
       <c r="G7" t="n">
-        <v>0.604182835882824</v>
+        <v>0.970876031195111</v>
       </c>
     </row>
     <row r="8">
@@ -630,16 +624,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00385026366526749</v>
+        <v>0.0121567785163433</v>
       </c>
       <c r="E8" t="n">
-        <v>0.58349158965515</v>
+        <v>1.80117416080727</v>
       </c>
       <c r="F8" t="n">
-        <v>0.560405062878427</v>
+        <v>0.0739582592993718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.809473979713283</v>
+        <v>0.578504951993659</v>
       </c>
     </row>
     <row r="9">
@@ -653,16 +647,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0123406906618065</v>
+        <v>-0.00251141094885521</v>
       </c>
       <c r="E9" t="n">
-        <v>1.87018080778624</v>
+        <v>-0.372095987614252</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0633323375370722</v>
+        <v>0.710418073150966</v>
       </c>
       <c r="G9" t="n">
-        <v>0.604182835882824</v>
+        <v>0.970876031195111</v>
       </c>
     </row>
     <row r="10">
@@ -676,16 +670,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00720560385648188</v>
+        <v>-0.00603780650654983</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0919795666388</v>
+        <v>-0.894574253609317</v>
       </c>
       <c r="F10" t="n">
-        <v>0.276525648956112</v>
+        <v>0.372642980839802</v>
       </c>
       <c r="G10" t="n">
-        <v>0.604182835882824</v>
+        <v>0.713126587662229</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0020840283132507</v>
+        <v>0.00506054066218526</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.31582590157511</v>
+        <v>0.749780467595814</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752556797697102</v>
+        <v>0.454721177478834</v>
       </c>
       <c r="G11" t="n">
-        <v>0.91390595889334</v>
+        <v>0.714561850323882</v>
       </c>
     </row>
     <row r="12">
@@ -722,62 +716,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0069881269152985</v>
+        <v>-0.00840425368311555</v>
       </c>
       <c r="E12" t="n">
-        <v>1.05902183253109</v>
+        <v>-1.24519210040279</v>
       </c>
       <c r="F12" t="n">
-        <v>0.291226844115223</v>
+        <v>0.215267106475554</v>
       </c>
       <c r="G12" t="n">
-        <v>0.604182835882824</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0049821094517022</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.755018153700315</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.451376452262867</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.733486734927159</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.00651074311506289</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.986676285137072</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.325329219321521</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.604182835882824</v>
+        <v>0.713126587662229</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +764,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -825,21 +773,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00000956064673086981</v>
+        <v>-0.0000114721586479905</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.240674299946708</v>
+        <v>-0.281366082966412</v>
       </c>
       <c r="F2" t="n">
-        <v>0.810123565431148</v>
+        <v>0.778870219950196</v>
       </c>
       <c r="G2" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -848,21 +796,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0000135365918507659</v>
+        <v>-0.0000323930866902034</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.340762488046768</v>
+        <v>-0.79447261817726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.733740870438725</v>
+        <v>0.42834640214606</v>
       </c>
       <c r="G3" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -871,21 +819,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00000940435430583081</v>
+        <v>-0.0000186944274992339</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.236739883056082</v>
+        <v>-0.458499398426674</v>
       </c>
       <c r="F4" t="n">
-        <v>0.813169172461613</v>
+        <v>0.647347686122711</v>
       </c>
       <c r="G4" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -894,21 +842,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000361873778556671</v>
+        <v>0.0000308184525236807</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.910960532010714</v>
+        <v>0.755853151594381</v>
       </c>
       <c r="F5" t="n">
-        <v>0.36372163200331</v>
+        <v>0.451083983016269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -917,21 +865,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000011549143338999</v>
+        <v>0.0000132591822845853</v>
       </c>
       <c r="E6" t="n">
-        <v>0.290731586088517</v>
+        <v>0.325194612210568</v>
       </c>
       <c r="F6" t="n">
-        <v>0.771642764858535</v>
+        <v>0.745548650464881</v>
       </c>
       <c r="G6" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -940,21 +888,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0000359274630952856</v>
+        <v>-0.00000927685159021496</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.904417585203712</v>
+        <v>-0.227523997382717</v>
       </c>
       <c r="F7" t="n">
-        <v>0.367168596542847</v>
+        <v>0.820368342166595</v>
       </c>
       <c r="G7" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -963,21 +911,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000114290156674558</v>
+        <v>0.0000336051916040157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.287707560197095</v>
+        <v>0.82420069483731</v>
       </c>
       <c r="F8" t="n">
-        <v>0.773952456348877</v>
+        <v>0.411312316797015</v>
       </c>
       <c r="G8" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -986,21 +934,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000370938942896807</v>
+        <v>-0.0000081284883224601</v>
       </c>
       <c r="E9" t="n">
-        <v>0.933780662728647</v>
+        <v>-0.199359247889187</v>
       </c>
       <c r="F9" t="n">
-        <v>0.35186012142103</v>
+        <v>0.842288505095398</v>
       </c>
       <c r="G9" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1009,21 +957,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000033588222829934</v>
+        <v>-0.000015211944946526</v>
       </c>
       <c r="E10" t="n">
-        <v>0.845530877105521</v>
+        <v>-0.3730880556341</v>
       </c>
       <c r="F10" t="n">
-        <v>0.39910950641747</v>
+        <v>0.709681355394209</v>
       </c>
       <c r="G10" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1032,21 +980,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0000212417230937468</v>
+        <v>0.0000123698960051626</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.534727093172724</v>
+        <v>0.303383983125452</v>
       </c>
       <c r="F11" t="n">
-        <v>0.593599907289223</v>
+        <v>0.762074896379942</v>
       </c>
       <c r="G11" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1055,62 +1003,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00000995964316092455</v>
+        <v>-0.0000105064529157575</v>
       </c>
       <c r="E12" t="n">
-        <v>0.250718409847202</v>
+        <v>-0.257681190914801</v>
       </c>
       <c r="F12" t="n">
-        <v>0.802361739925373</v>
+        <v>0.79705424970314</v>
       </c>
       <c r="G12" t="n">
-        <v>0.813169172461613</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0000124438246160778</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.313253785276267</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.754506283975184</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.813169172461613</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000243880099994357</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.613929935801895</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.540155860669386</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.813169172461613</v>
+        <v>0.842288505095398</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1051,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1158,21 +1060,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0000102541829771879</v>
+        <v>-0.0000198185759517381</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.24176182350583</v>
+        <v>-0.455547296626432</v>
       </c>
       <c r="F2" t="n">
-        <v>0.809282230055675</v>
+        <v>0.649464027112233</v>
       </c>
       <c r="G2" t="n">
-        <v>0.956424453702162</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1181,21 +1083,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000019403648592854</v>
+        <v>-0.0000416529190627549</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.457477838742564</v>
+        <v>-0.957428763895292</v>
       </c>
       <c r="F3" t="n">
-        <v>0.647964117010317</v>
+        <v>0.340101167139612</v>
       </c>
       <c r="G3" t="n">
-        <v>0.956424453702162</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1204,21 +1106,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00000150029291988496</v>
+        <v>-0.0000217062016168289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0353722527588193</v>
+        <v>-0.49893602298441</v>
       </c>
       <c r="F4" t="n">
-        <v>0.971828130762089</v>
+        <v>0.618654924919854</v>
       </c>
       <c r="G4" t="n">
-        <v>0.971828130762089</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1227,21 +1129,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000458362096824928</v>
+        <v>0.0000486797442411802</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.08067562867637</v>
+        <v>1.11894648452736</v>
       </c>
       <c r="F5" t="n">
-        <v>0.281509270882235</v>
+        <v>0.265195045112822</v>
       </c>
       <c r="G5" t="n">
-        <v>0.920942643986236</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1250,21 +1152,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000179199253016779</v>
+        <v>0.0000196971250292548</v>
       </c>
       <c r="E6" t="n">
-        <v>0.422496246425477</v>
+        <v>0.452755640982516</v>
       </c>
       <c r="F6" t="n">
-        <v>0.673244596882388</v>
+        <v>0.651467981379235</v>
       </c>
       <c r="G6" t="n">
-        <v>0.956424453702162</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1273,21 +1175,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0000413646742626004</v>
+        <v>-0.0000102915971166904</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.975250695320968</v>
+        <v>-0.236561358187066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.330945782523806</v>
+        <v>0.813363803305912</v>
       </c>
       <c r="G7" t="n">
-        <v>0.920942643986236</v>
+        <v>0.894700183636504</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1296,21 +1198,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00000204011380432869</v>
+        <v>0.0000360367497857587</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0480995545516568</v>
+        <v>0.828336202564835</v>
       </c>
       <c r="F8" t="n">
-        <v>0.961698425458297</v>
+        <v>0.408975323488623</v>
       </c>
       <c r="G8" t="n">
-        <v>0.971828130762089</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1319,21 +1221,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000394124723505742</v>
+        <v>-0.0000258624720904208</v>
       </c>
       <c r="E9" t="n">
-        <v>0.929223830464645</v>
+        <v>-0.594471533855816</v>
       </c>
       <c r="F9" t="n">
-        <v>0.354208709225476</v>
+        <v>0.553214340653229</v>
       </c>
       <c r="G9" t="n">
-        <v>0.920942643986236</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1342,21 +1244,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000507705938847213</v>
+        <v>-0.000032244176537409</v>
       </c>
       <c r="E10" t="n">
-        <v>1.19701310044404</v>
+        <v>-0.741160590414363</v>
       </c>
       <c r="F10" t="n">
-        <v>0.233117300710377</v>
+        <v>0.459912579119969</v>
       </c>
       <c r="G10" t="n">
-        <v>0.920942643986236</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1365,21 +1267,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.000023239260530796</v>
+        <v>0.000015789708166604</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.547909669190736</v>
+        <v>0.362940247943795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.584537060554249</v>
+        <v>0.717230041010914</v>
       </c>
       <c r="G11" t="n">
-        <v>0.956424453702162</v>
+        <v>0.876614494568895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1388,62 +1290,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000120492875693192</v>
+        <v>0.0000000457420710716477</v>
       </c>
       <c r="E12" t="n">
-        <v>0.284084820915065</v>
+        <v>0.00105142149817055</v>
       </c>
       <c r="F12" t="n">
-        <v>0.776722094046385</v>
+        <v>0.999162674506687</v>
       </c>
       <c r="G12" t="n">
-        <v>0.956424453702162</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0000159971088435538</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.377162199410978</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.706565651237239</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.956424453702162</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000457316200937596</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.07820973063767</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.282604548891969</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.920942643986236</v>
+        <v>0.999162674506687</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1338,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1491,21 +1347,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0101338863433553</v>
+        <v>-0.0197979682596668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.324034112339984</v>
+        <v>-0.623066776263026</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74634624586008</v>
+        <v>0.534774231863873</v>
       </c>
       <c r="G2" t="n">
-        <v>0.91103495081188</v>
+        <v>0.873354555056309</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1514,21 +1370,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0507379046603454</v>
+        <v>0.049865477677743</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.62236000499313</v>
+        <v>1.60301075493745</v>
       </c>
       <c r="F3" t="n">
-        <v>0.106745525495957</v>
+        <v>0.112342529506456</v>
       </c>
       <c r="G3" t="n">
-        <v>0.34692295786186</v>
+        <v>0.308941956142753</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1537,21 +1393,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.066546556007568</v>
+        <v>-0.0603206002847216</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.12784646231346</v>
+        <v>-1.88492308104354</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0349212729408908</v>
+        <v>0.0625803955116226</v>
       </c>
       <c r="G4" t="n">
-        <v>0.34692295786186</v>
+        <v>0.253559698498118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1560,21 +1416,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0534695514283276</v>
+        <v>-0.00350676550419551</v>
       </c>
       <c r="E5" t="n">
-        <v>1.70970524508158</v>
+        <v>-0.11109133757167</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0893086836883072</v>
+        <v>0.911784670997824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.34692295786186</v>
+        <v>0.946387155367039</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1583,21 +1439,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0111449064726858</v>
+        <v>-0.0115313136020025</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.356361789902725</v>
+        <v>-0.36685829503434</v>
       </c>
       <c r="F6" t="n">
-        <v>0.722051149259757</v>
+        <v>0.714562817773344</v>
       </c>
       <c r="G6" t="n">
-        <v>0.91103495081188</v>
+        <v>0.873354555056309</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1606,21 +1462,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0177960018151424</v>
+        <v>0.0118682724188549</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.56903259578705</v>
+        <v>0.389815078376337</v>
       </c>
       <c r="F7" t="n">
-        <v>0.570152371296844</v>
+        <v>0.697569629091197</v>
       </c>
       <c r="G7" t="n">
-        <v>0.91103495081188</v>
+        <v>0.873354555056309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1629,21 +1485,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0378693821559021</v>
+        <v>0.0579003977534304</v>
       </c>
       <c r="E8" t="n">
-        <v>1.21088506580669</v>
+        <v>1.83880913024514</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2277707320094</v>
+        <v>0.0691526450449414</v>
       </c>
       <c r="G8" t="n">
-        <v>0.592203903224441</v>
+        <v>0.253559698498118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1652,21 +1508,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0576566652971405</v>
+        <v>0.0168351774117431</v>
       </c>
       <c r="E9" t="n">
-        <v>1.84358949045176</v>
+        <v>0.517480063420662</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0671403060209308</v>
+        <v>0.606056717800678</v>
       </c>
       <c r="G9" t="n">
-        <v>0.34692295786186</v>
+        <v>0.873354555056309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1675,21 +1531,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.000586451130510893</v>
+        <v>-0.00226160021327571</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0187519540941445</v>
+        <v>-0.0674272359828316</v>
       </c>
       <c r="F10" t="n">
-        <v>0.985062944389025</v>
+        <v>0.946387155367039</v>
       </c>
       <c r="G10" t="n">
-        <v>0.985062944389025</v>
+        <v>0.946387155367039</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1698,21 +1554,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00101249631346554</v>
+        <v>0.0141231503242735</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0323748790015228</v>
+        <v>0.437567211772464</v>
       </c>
       <c r="F11" t="n">
-        <v>0.974214480338017</v>
+        <v>0.662720276135687</v>
       </c>
       <c r="G11" t="n">
-        <v>0.985062944389025</v>
+        <v>0.873354555056309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1721,62 +1577,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.034313837481119</v>
+        <v>-0.0665088601232832</v>
       </c>
       <c r="E12" t="n">
-        <v>1.09719543839796</v>
+        <v>-2.1738972182974</v>
       </c>
       <c r="F12" t="n">
-        <v>0.274246698587542</v>
+        <v>0.0322663036948152</v>
       </c>
       <c r="G12" t="n">
-        <v>0.594201180273008</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0133996948303802</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.428459336613331</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.668907736702974</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.91103495081188</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0091238046245587</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.291736440740803</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.770875727610052</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.91103495081188</v>
+        <v>0.253559698498118</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1824,21 +1634,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00106899408122537</v>
+        <v>-0.000930733213250018</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.586518970270218</v>
+        <v>-0.501592480612315</v>
       </c>
       <c r="F2" t="n">
-        <v>0.558374567593638</v>
+        <v>0.616789764136919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1847,21 +1657,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00000411907215110714</v>
+        <v>0.000381649863141823</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00225998815051134</v>
+        <v>0.205679456640637</v>
       </c>
       <c r="F3" t="n">
-        <v>0.998199679314496</v>
+        <v>0.837358173893184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1870,21 +1680,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000629041978578544</v>
+        <v>0.00057529816172906</v>
       </c>
       <c r="E4" t="n">
-        <v>0.34513292450573</v>
+        <v>0.310040759183554</v>
       </c>
       <c r="F4" t="n">
-        <v>0.730459349423073</v>
+        <v>0.757018911618229</v>
       </c>
       <c r="G4" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1893,21 +1703,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000624116843296979</v>
+        <v>0.00162517504243485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.342430678230919</v>
+        <v>0.875842367457393</v>
       </c>
       <c r="F5" t="n">
-        <v>0.732487734520426</v>
+        <v>0.382706742686862</v>
       </c>
       <c r="G5" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1916,21 +1726,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00135717710514098</v>
+        <v>-0.00125652871054259</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.744634729192463</v>
+        <v>-0.677170798150454</v>
       </c>
       <c r="F6" t="n">
-        <v>0.457612843079805</v>
+        <v>0.499482658025211</v>
       </c>
       <c r="G6" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1939,21 +1749,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000218853341154047</v>
+        <v>-0.00105509354731517</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.120077031808005</v>
+        <v>-0.568612983980512</v>
       </c>
       <c r="F7" t="n">
-        <v>0.90457663338046</v>
+        <v>0.570584935743868</v>
       </c>
       <c r="G7" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1962,21 +1772,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.000330541297328579</v>
+        <v>-0.00123754999191433</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.181356234562787</v>
+        <v>-0.666942751681208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8563233876711</v>
+        <v>0.505972858209094</v>
       </c>
       <c r="G8" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1985,21 +1795,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00108422264645878</v>
+        <v>0.000230163646011605</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.594874341507778</v>
+        <v>0.124040221737229</v>
       </c>
       <c r="F9" t="n">
-        <v>0.552789339576848</v>
+        <v>0.901472114381135</v>
       </c>
       <c r="G9" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2008,21 +1818,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00180768286151766</v>
+        <v>0.00246361302037433</v>
       </c>
       <c r="E10" t="n">
-        <v>0.991811188792664</v>
+        <v>1.32769492757578</v>
       </c>
       <c r="F10" t="n">
-        <v>0.322825525529478</v>
+        <v>0.186570389686241</v>
       </c>
       <c r="G10" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2031,21 +1841,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.000526749912771179</v>
+        <v>-0.00101405007158605</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.289008912073989</v>
+        <v>-0.546493757427895</v>
       </c>
       <c r="F11" t="n">
-        <v>0.772958260378237</v>
+        <v>0.585649144732559</v>
       </c>
       <c r="G11" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2054,62 +1864,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0000500073360010703</v>
+        <v>0.000657700483746347</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0274372437906145</v>
+        <v>0.354449172379144</v>
       </c>
       <c r="F12" t="n">
-        <v>0.978146060947011</v>
+        <v>0.723567900198723</v>
       </c>
       <c r="G12" t="n">
-        <v>0.998199679314496</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00105418694462299</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.578394821909431</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.56383165483005</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.998199679314496</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00197770372026536</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.08509557712422</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.279553348403053</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.998199679314496</v>
+        <v>0.901472114381135</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +1912,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -2157,21 +1921,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000953086431212725</v>
+        <v>-0.00534183608444658</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0924035663144863</v>
+        <v>-0.511946343553543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.926506732037615</v>
+        <v>0.60962167031674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.994836938508454</v>
+        <v>0.850531327020585</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -2180,21 +1944,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0110930572267377</v>
+        <v>-0.000800398474983556</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.07549327690771</v>
+        <v>-0.0767079083251419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.283965170723443</v>
+        <v>0.938982605321297</v>
       </c>
       <c r="G3" t="n">
-        <v>0.735356598978484</v>
+        <v>0.971485824851605</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -2203,21 +1967,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00916933259221759</v>
+        <v>-0.0149274438031787</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.888984466148012</v>
+        <v>-1.43060366376443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.37550441104881</v>
+        <v>0.155121246122429</v>
       </c>
       <c r="G4" t="n">
-        <v>0.735356598978484</v>
+        <v>0.568777902448905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -2226,21 +1990,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000668610360934801</v>
+        <v>0.000373747056392927</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0064823063052717</v>
+        <v>0.0358188525273856</v>
       </c>
       <c r="F5" t="n">
-        <v>0.994836938508454</v>
+        <v>0.971485824851605</v>
       </c>
       <c r="G5" t="n">
-        <v>0.994836938508454</v>
+        <v>0.971485824851605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -2249,21 +2013,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00878184776028905</v>
+        <v>0.00775250508088794</v>
       </c>
       <c r="E6" t="n">
-        <v>0.851417064923542</v>
+        <v>0.742977988616441</v>
       </c>
       <c r="F6" t="n">
-        <v>0.395961245603799</v>
+        <v>0.458935074582038</v>
       </c>
       <c r="G6" t="n">
-        <v>0.735356598978484</v>
+        <v>0.850531327020585</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -2272,21 +2036,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0114587362686396</v>
+        <v>-0.00103666213395655</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.11094656476451</v>
+        <v>-0.0993507439370356</v>
       </c>
       <c r="F7" t="n">
-        <v>0.268455800902638</v>
+        <v>0.921024201141512</v>
       </c>
       <c r="G7" t="n">
-        <v>0.735356598978484</v>
+        <v>0.971485824851605</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -2295,21 +2059,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00158615730707879</v>
+        <v>0.0162373691732823</v>
       </c>
       <c r="E8" t="n">
-        <v>0.153781007797339</v>
+        <v>1.55614317732329</v>
       </c>
       <c r="F8" t="n">
-        <v>0.877999216137534</v>
+        <v>0.122285796582151</v>
       </c>
       <c r="G8" t="n">
-        <v>0.994836938508454</v>
+        <v>0.568777902448905</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -2318,21 +2082,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0161948541437392</v>
+        <v>-0.00520848954426146</v>
       </c>
       <c r="E9" t="n">
-        <v>1.57012232030238</v>
+        <v>-0.49916679124342</v>
       </c>
       <c r="F9" t="n">
-        <v>0.118596741239331</v>
+        <v>0.618568237833153</v>
       </c>
       <c r="G9" t="n">
-        <v>0.735356598978484</v>
+        <v>0.850531327020585</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -2341,21 +2105,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.000214969856477233</v>
+        <v>-0.0205262767850049</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0208417418799409</v>
+        <v>-1.96717985739915</v>
       </c>
       <c r="F10" t="n">
-        <v>0.983400952631196</v>
+        <v>0.0514508161536453</v>
       </c>
       <c r="G10" t="n">
-        <v>0.994836938508454</v>
+        <v>0.565958977690098</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -2364,21 +2128,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00462718121073209</v>
+        <v>0.0127824895932231</v>
       </c>
       <c r="E11" t="n">
-        <v>0.448614135982381</v>
+        <v>1.2250373664245</v>
       </c>
       <c r="F11" t="n">
-        <v>0.654389078447607</v>
+        <v>0.222940531639449</v>
       </c>
       <c r="G11" t="n">
-        <v>0.994836938508454</v>
+        <v>0.613086462008485</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -2387,62 +2151,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00111298625405492</v>
+        <v>-0.00725086831226831</v>
       </c>
       <c r="E12" t="n">
-        <v>0.107906162301372</v>
+        <v>-0.694902550615905</v>
       </c>
       <c r="F12" t="n">
-        <v>0.914221381636003</v>
+        <v>0.488448634880821</v>
       </c>
       <c r="G12" t="n">
-        <v>0.994836938508454</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0127982591186453</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.24081588662945</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.216705566511415</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.735356598978484</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.017575919626859</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.70401928050958</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.090549459633892</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.735356598978484</v>
+        <v>0.850531327020585</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2199,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2490,21 +2208,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0249874931003802</v>
+        <v>-0.0219839407871226</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.215025680833449</v>
+        <v>-0.184440840054396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.830028145338985</v>
+        <v>0.853950694051959</v>
       </c>
       <c r="G2" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2513,21 +2231,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0740206856492288</v>
+        <v>0.00343100088507379</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.63697259519171</v>
+        <v>0.0287854071114069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.525076334871694</v>
+        <v>0.977079214809522</v>
       </c>
       <c r="G3" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2536,21 +2254,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.128704067913617</v>
+        <v>-0.0935516414963636</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.10754126946567</v>
+        <v>-0.784879449646453</v>
       </c>
       <c r="F4" t="n">
-        <v>0.269764752708905</v>
+        <v>0.433930640734087</v>
       </c>
       <c r="G4" t="n">
-        <v>0.927792912821149</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2559,21 +2277,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0212153308393172</v>
+        <v>0.0468110455888256</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.182564971183989</v>
+        <v>0.392735254149021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.855376407807058</v>
+        <v>0.695148519056304</v>
       </c>
       <c r="G5" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2582,21 +2300,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0118388352690944</v>
+        <v>0.0169886452861274</v>
       </c>
       <c r="E6" t="n">
-        <v>0.101877111232633</v>
+        <v>0.14253131585011</v>
       </c>
       <c r="F6" t="n">
-        <v>0.918985048585734</v>
+        <v>0.886877674689093</v>
       </c>
       <c r="G6" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2605,21 +2323,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0384367287846884</v>
+        <v>-0.0205877758799003</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.330760822733853</v>
+        <v>-0.172727297389953</v>
       </c>
       <c r="F7" t="n">
-        <v>0.741268989401802</v>
+        <v>0.863130350884894</v>
       </c>
       <c r="G7" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2628,21 +2346,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.124548202530547</v>
+        <v>0.204476419141905</v>
       </c>
       <c r="E8" t="n">
-        <v>1.07177866695662</v>
+        <v>1.71551601612478</v>
       </c>
       <c r="F8" t="n">
-        <v>0.285474742406507</v>
+        <v>0.088596966540912</v>
       </c>
       <c r="G8" t="n">
-        <v>0.927792912821149</v>
+        <v>0.974566631950031</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2651,21 +2369,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.19695404121633</v>
+        <v>0.0314785154040241</v>
       </c>
       <c r="E9" t="n">
-        <v>1.69485496745554</v>
+        <v>0.264098410790132</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0920981576061795</v>
+        <v>0.792115968292707</v>
       </c>
       <c r="G9" t="n">
-        <v>0.927792912821149</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2674,21 +2392,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0571349411295765</v>
+        <v>-0.0239887874837593</v>
       </c>
       <c r="E10" t="n">
-        <v>0.491665152899203</v>
+        <v>-0.201261100465785</v>
       </c>
       <c r="F10" t="n">
-        <v>0.623647162077209</v>
+        <v>0.840804221787</v>
       </c>
       <c r="G10" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2697,21 +2415,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00973887672055086</v>
+        <v>-0.000776217836797531</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0838062701599149</v>
+        <v>-0.00651231147638481</v>
       </c>
       <c r="F11" t="n">
-        <v>0.933317909594904</v>
+        <v>0.994813795793276</v>
       </c>
       <c r="G11" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2720,62 +2438,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.128878981959794</v>
+        <v>-0.142853706654739</v>
       </c>
       <c r="E12" t="n">
-        <v>1.10904646295249</v>
+        <v>-1.19851385679305</v>
       </c>
       <c r="F12" t="n">
-        <v>0.269116935237505</v>
+        <v>0.232864364125847</v>
       </c>
       <c r="G12" t="n">
-        <v>0.927792912821149</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.00158606806179534</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.0136486426815878</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.989127736344026</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.989127736344026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0349023482953468</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.300346304238856</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.764312890692445</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.989127736344026</v>
+        <v>0.994813795793276</v>
       </c>
     </row>
   </sheetData>
@@ -2791,45 +2463,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2838,24 +2510,24 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00651074311506289</v>
+        <v>0.00583363322851157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2864,24 +2536,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00878184776028905</v>
+        <v>0.00725086831226831</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2890,24 +2562,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000629041978578544</v>
+        <v>0.00101405007158605</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2916,24 +2588,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000135365918507659</v>
+        <v>0.0000132591822845853</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2942,24 +2614,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000019403648592854</v>
+        <v>0.0000217062016168289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2968,24 +2640,24 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0177960018151424</v>
+        <v>0.0168351774117431</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2994,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0384367287846884</v>
+        <v>0.0239887874837593</v>
       </c>
     </row>
   </sheetData>
